--- a/Homeworks/HW_5/HW_5.xlsx
+++ b/Homeworks/HW_5/HW_5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harrisonknight/Documents/School/College - DU/Sophomore Year/Fall Quarter/ENCE 2101/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harrisonknight/Documents/School/College - DU/Sophomore Year/Fall Quarter/ENCE_2101/Homeworks/HW_5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{15456059-659D-4648-9FF8-94D0ADB9C000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D55388B1-B1EB-A44D-A950-37B873994331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="760" windowWidth="28040" windowHeight="17160" xr2:uid="{DBD1D292-92E0-6548-AE56-0A6AD261285A}"/>
+    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17100" xr2:uid="{109671D8-1CFD-944A-AFAE-D335DB82338D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="12">
   <si>
     <t>A</t>
   </si>
@@ -50,32 +50,48 @@
     <t>C</t>
   </si>
   <si>
-    <t>L1</t>
+    <t>f</t>
   </si>
   <si>
-    <t>L2</t>
+    <t>B+C'</t>
   </si>
   <si>
-    <t>L3</t>
+    <t>BC'</t>
   </si>
   <si>
-    <t>L4</t>
+    <t>(B+C)'</t>
   </si>
   <si>
-    <t>L5</t>
+    <t>(B+C')</t>
   </si>
   <si>
-    <t>x</t>
+    <t>(BC')</t>
+  </si>
+  <si>
+    <t>C'</t>
+  </si>
+  <si>
+    <t>B'</t>
+  </si>
+  <si>
+    <t>(B ^ C)'</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -89,7 +105,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -98,6 +114,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -234,7 +270,7 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -247,7 +283,7 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="thin">
@@ -260,13 +296,44 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -275,7 +342,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -289,6 +356,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -622,250 +696,635 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88D00290-8C48-C647-87DA-9146BC9A3588}">
-  <dimension ref="B3:I12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="2" customWidth="1"/>
-    <col min="3" max="4" width="2.5" customWidth="1"/>
-    <col min="5" max="6" width="3" customWidth="1"/>
-    <col min="7" max="8" width="3.33203125" customWidth="1"/>
-    <col min="9" max="9" width="3.1640625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF852091-8443-B24C-A2C5-C592F7FD78A4}">
+  <dimension ref="D4:BM13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="3" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="3" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4" t="s">
+    <row r="4" spans="4:65" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="4:65" x14ac:dyDescent="0.2">
+      <c r="D5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="G5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="N5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD5" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ5" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="BC5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE5" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="4:65" x14ac:dyDescent="0.2">
+      <c r="D6" s="7">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="8">
+        <v>0</v>
+      </c>
+      <c r="G6" s="13">
+        <v>0</v>
+      </c>
+      <c r="N6" s="7">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3">
+        <v>0</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="13">
+        <v>1</v>
+      </c>
+      <c r="AN6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="13">
+        <v>1</v>
+      </c>
+      <c r="BB6" s="7">
+        <v>0</v>
+      </c>
+      <c r="BC6" s="3">
+        <v>0</v>
+      </c>
+      <c r="BD6" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE6" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="4:65" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="7">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="8">
+        <v>1</v>
+      </c>
+      <c r="G7" s="13">
+        <v>1</v>
+      </c>
+      <c r="N7" s="7">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3">
+        <v>0</v>
+      </c>
+      <c r="P7" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="13">
+        <v>0</v>
+      </c>
+      <c r="S7" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="AA7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="8">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>6</v>
+      </c>
+      <c r="AN7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="8">
+        <v>1</v>
+      </c>
+      <c r="AQ7" s="13">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB7" s="7">
+        <v>0</v>
+      </c>
+      <c r="BC7" s="3">
+        <v>0</v>
+      </c>
+      <c r="BD7" s="8">
+        <v>1</v>
+      </c>
+      <c r="BE7" s="13">
+        <v>1</v>
+      </c>
+      <c r="BF7" s="1"/>
+      <c r="BG7" s="2"/>
+      <c r="BH7" s="2">
+        <v>1</v>
+      </c>
+      <c r="BI7" s="2"/>
+    </row>
+    <row r="8" spans="4:65" x14ac:dyDescent="0.2">
+      <c r="D8" s="7">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+      <c r="F8" s="8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="13">
+        <v>1</v>
+      </c>
+      <c r="N8" s="7">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
+        <v>1</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="13">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AP8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="13">
+        <v>1</v>
+      </c>
+      <c r="BB8" s="7">
+        <v>0</v>
+      </c>
+      <c r="BC8" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD8" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE8" s="13">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="4:65" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D9" s="7">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
+      <c r="F9" s="8">
+        <v>1</v>
+      </c>
+      <c r="G9" s="13">
+        <v>1</v>
+      </c>
+      <c r="N9" s="7">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3">
+        <v>1</v>
+      </c>
+      <c r="P9" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="13">
+        <v>1</v>
+      </c>
+      <c r="R9" s="15"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="16"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="16"/>
+      <c r="AA9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="8">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="15"/>
+      <c r="AF9" s="16"/>
+      <c r="AG9" s="16"/>
+      <c r="AH9" s="16"/>
+      <c r="AI9" s="16"/>
+      <c r="AJ9" s="16"/>
+      <c r="AN9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="3">
+        <v>1</v>
+      </c>
+      <c r="AP9" s="8">
+        <v>1</v>
+      </c>
+      <c r="AQ9" s="13">
+        <v>1</v>
+      </c>
+      <c r="AR9" s="15"/>
+      <c r="AS9" s="16"/>
+      <c r="AT9" s="16"/>
+      <c r="AU9" s="16"/>
+      <c r="AV9" s="16"/>
+      <c r="AW9" s="16"/>
+      <c r="AX9" s="16"/>
+      <c r="BB9" s="7">
+        <v>0</v>
+      </c>
+      <c r="BC9" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD9" s="8">
+        <v>1</v>
+      </c>
+      <c r="BE9" s="13">
+        <v>0</v>
+      </c>
+      <c r="BF9" s="1"/>
+      <c r="BG9" s="2"/>
+      <c r="BH9" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI9" s="2"/>
+      <c r="BJ9" s="19"/>
+      <c r="BK9" s="18"/>
+      <c r="BL9" s="18"/>
+      <c r="BM9" s="18"/>
+    </row>
+    <row r="10" spans="4:65" x14ac:dyDescent="0.2">
+      <c r="D10" s="7">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0</v>
+      </c>
+      <c r="G10" s="13">
+        <v>0</v>
+      </c>
+      <c r="N10" s="7">
+        <v>1</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="13">
+        <v>1</v>
+      </c>
+      <c r="AN10" s="7">
+        <v>1</v>
+      </c>
+      <c r="AO10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="13">
+        <v>0</v>
+      </c>
+      <c r="BB10" s="7">
+        <v>1</v>
+      </c>
+      <c r="BC10" s="3">
+        <v>0</v>
+      </c>
+      <c r="BD10" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE10" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="4:65" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D11" s="7">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="8">
+        <v>1</v>
+      </c>
+      <c r="G11" s="13">
+        <v>1</v>
+      </c>
+      <c r="N11" s="7">
+        <v>1</v>
+      </c>
+      <c r="O11" s="3">
+        <v>0</v>
+      </c>
+      <c r="P11" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="13">
+        <v>0</v>
+      </c>
+      <c r="S11" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="4" t="s">
+      <c r="AA11" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="8">
+        <v>1</v>
+      </c>
+      <c r="AD11" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="s">
         <v>7</v>
       </c>
+      <c r="AN11" s="7">
+        <v>1</v>
+      </c>
+      <c r="AO11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="8">
+        <v>1</v>
+      </c>
+      <c r="AQ11" s="13">
+        <v>0</v>
+      </c>
+      <c r="BB11" s="7">
+        <v>1</v>
+      </c>
+      <c r="BC11" s="3">
+        <v>0</v>
+      </c>
+      <c r="BD11" s="8">
+        <v>1</v>
+      </c>
+      <c r="BE11" s="17">
+        <v>0</v>
+      </c>
+      <c r="BF11" s="1"/>
+      <c r="BG11" s="2"/>
+      <c r="BH11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="BI11" s="2"/>
+      <c r="BK11" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B5" s="5">
-        <v>0</v>
-      </c>
-      <c r="C5" s="1">
-        <v>0</v>
-      </c>
-      <c r="D5" s="6">
-        <v>0</v>
-      </c>
-      <c r="E5" s="11">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6">
+    <row r="12" spans="4:65" x14ac:dyDescent="0.2">
+      <c r="D12" s="7">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="8">
+        <v>0</v>
+      </c>
+      <c r="G12" s="13">
+        <v>1</v>
+      </c>
+      <c r="N12" s="7">
+        <v>1</v>
+      </c>
+      <c r="O12" s="3">
+        <v>1</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="13">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="13">
+        <v>1</v>
+      </c>
+      <c r="AN12" s="7">
+        <v>1</v>
+      </c>
+      <c r="AO12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AP12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="13">
+        <v>1</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>8</v>
+      </c>
+      <c r="BB12" s="7">
+        <v>1</v>
+      </c>
+      <c r="BC12" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD12" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE12" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B6" s="5">
-        <v>0</v>
-      </c>
-      <c r="C6" s="1">
-        <v>0</v>
-      </c>
-      <c r="D6" s="6">
-        <v>1</v>
-      </c>
-      <c r="E6" s="11">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B7" s="5">
-        <v>0</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0</v>
-      </c>
-      <c r="E7" s="11">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B8" s="5">
-        <v>0</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1</v>
-      </c>
-      <c r="D8" s="6">
-        <v>1</v>
-      </c>
-      <c r="E8" s="11">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B9" s="5">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1">
-        <v>0</v>
-      </c>
-      <c r="D9" s="6">
-        <v>0</v>
-      </c>
-      <c r="E9" s="11">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1</v>
-      </c>
-      <c r="H9" s="1">
-        <v>1</v>
-      </c>
-      <c r="I9" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B10" s="5">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1">
-        <v>0</v>
-      </c>
-      <c r="D10" s="6">
-        <v>1</v>
-      </c>
-      <c r="E10" s="11">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1</v>
-      </c>
-      <c r="H10" s="1">
-        <v>1</v>
-      </c>
-      <c r="I10" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B11" s="5">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1</v>
-      </c>
-      <c r="D11" s="6">
-        <v>0</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="7">
-        <v>1</v>
-      </c>
-      <c r="C12" s="8">
-        <v>1</v>
-      </c>
-      <c r="D12" s="9">
-        <v>1</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>8</v>
+    <row r="13" spans="4:65" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D13" s="9">
+        <v>1</v>
+      </c>
+      <c r="E13" s="10">
+        <v>1</v>
+      </c>
+      <c r="F13" s="11">
+        <v>1</v>
+      </c>
+      <c r="G13" s="14">
+        <v>0</v>
+      </c>
+      <c r="N13" s="9">
+        <v>1</v>
+      </c>
+      <c r="O13" s="10">
+        <v>1</v>
+      </c>
+      <c r="P13" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="10">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="11">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="14">
+        <v>1</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>1</v>
+      </c>
+      <c r="AO13" s="10">
+        <v>1</v>
+      </c>
+      <c r="AP13" s="11">
+        <v>1</v>
+      </c>
+      <c r="AQ13" s="14">
+        <v>0</v>
+      </c>
+      <c r="BB13" s="9">
+        <v>1</v>
+      </c>
+      <c r="BC13" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD13" s="11">
+        <v>1</v>
+      </c>
+      <c r="BE13" s="14">
+        <v>1</v>
+      </c>
+      <c r="BH13" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
